--- a/data/parcours.xlsx
+++ b/data/parcours.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>lieu</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>acteur</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -526,11 +521,6 @@
           <t>Urgences</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Dr Aubert</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,11 +568,6 @@
           <t>Cardiologie — Ch. 214</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Équipe Cardiologie</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -630,11 +615,6 @@
           <t>Plateau technique cardio</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Dr Bianchi</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -682,11 +662,6 @@
           <t>Cardiologie — Ch. 214</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>IDE Roussel</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -734,11 +709,6 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -786,11 +756,6 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -838,11 +803,6 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -890,11 +850,6 @@
           <t>Salle de cathétérisme</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Dr Perrot</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -942,11 +897,6 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -994,11 +944,6 @@
           <t>Urgences</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Dr Caron</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1046,11 +991,6 @@
           <t>Imagerie</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Dr Roche</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1098,11 +1038,6 @@
           <t>Pneumologie</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1150,11 +1085,6 @@
           <t>Pneumologie</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1202,11 +1132,6 @@
           <t>Pneumologie</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1254,11 +1179,6 @@
           <t>Urgences</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Dr Caron</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1306,11 +1226,6 @@
           <t>Imagerie</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Dr Roche</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1358,11 +1273,6 @@
           <t>Pneumologie</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1410,11 +1320,6 @@
           <t>Chirurgie orthopédique</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1462,11 +1367,6 @@
           <t>Bloc opératoire</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1514,11 +1414,6 @@
           <t>Chirurgie orthopédique</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1566,11 +1461,6 @@
           <t>Plateau de rééducation</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Kinésithérapeute Ferry</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1618,11 +1508,6 @@
           <t>Chirurgie orthopédique</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1670,11 +1555,6 @@
           <t>Consultation ortho</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1720,11 +1600,6 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>Imagerie</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Dr Roche</t>
         </is>
       </c>
     </row>

--- a/data/parcours.xlsx
+++ b/data/parcours.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>lieu</t>
+          <t>uf</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Urgences</t>
+          <t>UF Urgences</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cardiologie — Ch. 214</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Plateau technique cardio</t>
+          <t>UF Imagerie cardiaque</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cardiologie — Ch. 214</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Salle de cathétérisme</t>
+          <t>UF Cardiologie interventionnelle</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Urgences</t>
+          <t>UF Urgences</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Imagerie</t>
+          <t>UF Imagerie</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000077</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Urgences</t>
+          <t>UF Urgences</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000077</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Imagerie</t>
+          <t>UF Imagerie</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000077</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Chirurgie orthopédique</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bloc opératoire</t>
+          <t>UF Bloc opératoire</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chirurgie orthopédique</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Plateau de rééducation</t>
+          <t>UF Rééducation</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Chirurgie orthopédique</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000142</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Consultation ortho</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000142</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Imagerie</t>
+          <t>UF Imagerie</t>
         </is>
       </c>
     </row>
